--- a/templates/summary_template_simplified.xlsx
+++ b/templates/summary_template_simplified.xlsx
@@ -1056,7 +1056,7 @@
       <x:c r="C10" s="45" t="n"/>
       <x:c r="D10" s="28" t="n"/>
       <x:c r="E10" s="41" t="str">
-        <x:f>IF(AND(C10&lt;&gt;0,F10&lt;&gt;0),F10/C10*100,"")</x:f>
+        <x:f>IF(AND(C10&lt;&gt;0,F10&lt;&gt;0),F10/C10,"")</x:f>
       </x:c>
       <x:c r="F10" s="42" t="n"/>
       <x:c r="G10" s="43" t="n"/>
